--- a/注塑项目/金榕/GEA轮罩 /GEA轮罩气坝-内部报价格式-260630_第三版.xlsx
+++ b/注塑项目/金榕/GEA轮罩 /GEA轮罩气坝-内部报价格式-260630_第三版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chensiyuan5/Desktop/Github/shenyuan_work/注塑项目/金榕/GEA轮罩 /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E199879C-F5FB-4C4A-AFD4-79B851529850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80DD88D4-3FC4-544E-B973-1774C67B5573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1100" windowWidth="30240" windowHeight="13800" tabRatio="566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3500" yWindow="1100" windowWidth="35340" windowHeight="20120" tabRatio="566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="81">
   <si>
     <t>GEA轮罩气坝内部报价 · 2026-06-30</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>06-30 极限报价</t>
+  </si>
+  <si>
+    <t>模具取数更正</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1085,6 +1088,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="8" fontId="4" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1101,12 +1111,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1678,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BL24"/>
+  <dimension ref="A1:BL37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="73" customWidth="1"/>
@@ -1700,14 +1706,14 @@
       <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="159" t="s">
+      <c r="E1" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
@@ -1766,12 +1772,12 @@
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="E2" s="163"/>
+      <c r="F2" s="163"/>
+      <c r="G2" s="163"/>
+      <c r="H2" s="163"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -1801,33 +1807,33 @@
       <c r="AK2" s="19"/>
       <c r="AL2" s="19"/>
       <c r="AM2" s="19"/>
-      <c r="AN2" s="163" t="s">
+      <c r="AN2" s="158" t="s">
         <v>3</v>
       </c>
-      <c r="AO2" s="162"/>
+      <c r="AO2" s="157"/>
       <c r="AP2" s="19"/>
       <c r="AQ2" s="19"/>
       <c r="AR2" s="9"/>
-      <c r="AS2" s="161" t="s">
+      <c r="AS2" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="AT2" s="162"/>
-      <c r="AU2" s="161" t="s">
+      <c r="AT2" s="157"/>
+      <c r="AU2" s="156" t="s">
         <v>5</v>
       </c>
-      <c r="AV2" s="162"/>
-      <c r="AW2" s="161" t="s">
+      <c r="AV2" s="157"/>
+      <c r="AW2" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="AX2" s="162"/>
-      <c r="AY2" s="161" t="s">
+      <c r="AX2" s="157"/>
+      <c r="AY2" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="162"/>
-      <c r="BA2" s="161" t="s">
+      <c r="AZ2" s="157"/>
+      <c r="BA2" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="162"/>
+      <c r="BB2" s="157"/>
       <c r="BC2" s="20"/>
       <c r="BD2" s="21"/>
       <c r="BE2" s="21"/>
@@ -3196,22 +3202,22 @@
       </c>
     </row>
     <row r="10" spans="1:64" ht="28" customHeight="1">
-      <c r="A10" s="156" t="s">
+      <c r="A10" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="157"/>
-      <c r="H10" s="157"/>
-      <c r="I10" s="157"/>
-      <c r="J10" s="157"/>
-      <c r="K10" s="157"/>
-      <c r="L10" s="157"/>
-      <c r="M10" s="157"/>
-      <c r="N10" s="158"/>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
+      <c r="L10" s="160"/>
+      <c r="M10" s="160"/>
+      <c r="N10" s="161"/>
       <c r="O10" s="80"/>
       <c r="P10" s="81"/>
       <c r="Q10" s="155"/>
@@ -5742,6 +5748,935 @@
         <v>1228338.3555396481</v>
       </c>
     </row>
+    <row r="30" spans="1:64">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:64" s="3" customFormat="1" ht="73.25" customHeight="1">
+      <c r="A31" s="22">
+        <v>0</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="O31" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="T31" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="U31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="V31" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="W31" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="X31" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y31" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB31" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC31" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD31" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE31" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ31" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK31" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL31" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM31" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN31" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO31" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP31" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ31" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR31" s="28"/>
+      <c r="AS31" s="29"/>
+      <c r="AT31" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU31" s="29"/>
+      <c r="AV31" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW31" s="29"/>
+      <c r="AX31" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY31" s="29"/>
+      <c r="AZ31" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA31" s="29"/>
+      <c r="BB31" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC31" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD31" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="BE31" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF31" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="BG31" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH31" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI31" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ31" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="BK31" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL31" s="32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:64" ht="72">
+      <c r="A32" s="33">
+        <v>1</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="38">
+        <v>2</v>
+      </c>
+      <c r="H32" s="39">
+        <v>2</v>
+      </c>
+      <c r="I32" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="J32" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="K32" s="42">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L32" s="43">
+        <v>8</v>
+      </c>
+      <c r="M32" s="44">
+        <f t="shared" ref="M32:M37" si="76">ROUND(K32/L32/12*10000,-2)</f>
+        <v>6400</v>
+      </c>
+      <c r="N32" s="45">
+        <v>77</v>
+      </c>
+      <c r="O32" s="46">
+        <v>11.7</v>
+      </c>
+      <c r="P32" s="47">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="48"/>
+      <c r="R32" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S32" s="50">
+        <f t="shared" ref="S32:S37" si="77">(N32+O32*(1-P32)/H32)*(1+Q32)+R32/M32</f>
+        <v>86.756249999999994</v>
+      </c>
+      <c r="T32" s="46">
+        <v>18</v>
+      </c>
+      <c r="U32" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="V32" s="52">
+        <f>(S32*T32/1000)*(1+U32)</f>
+        <v>1.5772286249999998</v>
+      </c>
+      <c r="W32" s="53">
+        <v>360</v>
+      </c>
+      <c r="X32" s="54">
+        <v>50</v>
+      </c>
+      <c r="Y32" s="55">
+        <v>1.7728999999999999</v>
+      </c>
+      <c r="Z32" s="56">
+        <f t="shared" ref="Z32:Z37" si="78">Y32/60/0.9</f>
+        <v>3.2831481481481482E-2</v>
+      </c>
+      <c r="AA32" s="57">
+        <f t="shared" ref="AA32:AA37" si="79">U32</f>
+        <v>0.01</v>
+      </c>
+      <c r="AB32" s="56">
+        <f>(Z32*X32/H32)*(1+AA32)</f>
+        <v>0.82899490740740744</v>
+      </c>
+      <c r="AC32" s="56">
+        <f t="shared" ref="AC32:AC37" si="80">V32*0.03</f>
+        <v>4.7316858749999996E-2</v>
+      </c>
+      <c r="AD32" s="56">
+        <f t="shared" ref="AD32:AD37" si="81">(AB32)*0.08</f>
+        <v>6.6319592592592597E-2</v>
+      </c>
+      <c r="AE32" s="58">
+        <v>0.32</v>
+      </c>
+      <c r="AF32" s="57">
+        <f t="shared" ref="AF32:AF37" si="82">AE32/$AL32</f>
+        <v>8.5728828973264837E-2</v>
+      </c>
+      <c r="AG32" s="58">
+        <v>0.2</v>
+      </c>
+      <c r="AH32" s="57">
+        <f t="shared" ref="AH32:AH37" si="83">AG32/$AL32</f>
+        <v>5.3580518108290523E-2</v>
+      </c>
+      <c r="AI32" s="56">
+        <f>(AB32+AC32+AD32+AE32+AG32+V32)*15%</f>
+        <v>0.45597899756249993</v>
+      </c>
+      <c r="AJ32" s="59">
+        <v>217500</v>
+      </c>
+      <c r="AK32" s="56">
+        <f>AJ32/918260</f>
+        <v>0.23686101975475354</v>
+      </c>
+      <c r="AL32" s="60">
+        <f t="shared" ref="AL32:AL37" si="84">SUM($V32+$AB32+$AC32+$AD32+$AE32+$AG32+$AI32+$AK32)</f>
+        <v>3.7327000010672533</v>
+      </c>
+      <c r="AQ32" s="164">
+        <f>V32/AL32</f>
+        <v>0.42254363451363325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" ht="72">
+      <c r="A33" s="74">
+        <v>2</v>
+      </c>
+      <c r="B33" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="38">
+        <v>2</v>
+      </c>
+      <c r="H33" s="77">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>1.5</v>
+      </c>
+      <c r="J33" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K33" s="77">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L33" s="78">
+        <v>8</v>
+      </c>
+      <c r="M33" s="77">
+        <f t="shared" si="76"/>
+        <v>6400</v>
+      </c>
+      <c r="N33" s="79">
+        <v>77</v>
+      </c>
+      <c r="O33" s="80">
+        <v>11.7</v>
+      </c>
+      <c r="P33" s="81">
+        <v>0</v>
+      </c>
+      <c r="R33" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S33" s="83">
+        <f t="shared" si="77"/>
+        <v>86.756249999999994</v>
+      </c>
+      <c r="T33" s="46">
+        <v>18</v>
+      </c>
+      <c r="U33" s="84">
+        <v>0.01</v>
+      </c>
+      <c r="V33" s="85">
+        <f>(S33*T33/1000)*(1+U33)</f>
+        <v>1.5772286249999998</v>
+      </c>
+      <c r="W33" s="53">
+        <v>360</v>
+      </c>
+      <c r="X33" s="54">
+        <v>50</v>
+      </c>
+      <c r="Y33" s="55">
+        <v>1.7728999999999999</v>
+      </c>
+      <c r="Z33" s="86">
+        <f t="shared" si="78"/>
+        <v>3.2831481481481482E-2</v>
+      </c>
+      <c r="AA33" s="87">
+        <f t="shared" si="79"/>
+        <v>0.01</v>
+      </c>
+      <c r="AB33" s="86">
+        <f t="shared" ref="AB33:AB37" si="85">(Z33*X33/H33)*(1+AA33)</f>
+        <v>0.82899490740740744</v>
+      </c>
+      <c r="AC33" s="86">
+        <f t="shared" si="80"/>
+        <v>4.7316858749999996E-2</v>
+      </c>
+      <c r="AD33" s="86">
+        <f t="shared" si="81"/>
+        <v>6.6319592592592597E-2</v>
+      </c>
+      <c r="AE33" s="58">
+        <v>0.42</v>
+      </c>
+      <c r="AF33" s="87">
+        <f t="shared" si="82"/>
+        <v>0.10598834125391364</v>
+      </c>
+      <c r="AG33" s="58">
+        <v>0.3</v>
+      </c>
+      <c r="AH33" s="87">
+        <f t="shared" si="83"/>
+        <v>7.5705958038509741E-2</v>
+      </c>
+      <c r="AI33" s="86">
+        <f t="shared" ref="AI32:AI37" si="86">(AB33+AC33+AD33+AE33+AG33+V33)*15%</f>
+        <v>0.48597899756249996</v>
+      </c>
+      <c r="AJ33" s="59">
+        <v>217500</v>
+      </c>
+      <c r="AK33" s="56">
+        <f>AJ33/918260</f>
+        <v>0.23686101975475354</v>
+      </c>
+      <c r="AL33" s="90">
+        <f t="shared" si="84"/>
+        <v>3.9627000010672533</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" ht="72">
+      <c r="A34" s="74">
+        <v>3</v>
+      </c>
+      <c r="B34" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="38">
+        <v>2</v>
+      </c>
+      <c r="H34" s="77">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>1.5</v>
+      </c>
+      <c r="J34" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="77">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L34" s="78">
+        <v>8</v>
+      </c>
+      <c r="M34" s="77">
+        <f t="shared" si="76"/>
+        <v>6400</v>
+      </c>
+      <c r="N34" s="79">
+        <v>78</v>
+      </c>
+      <c r="O34" s="80">
+        <v>11.7</v>
+      </c>
+      <c r="P34" s="81">
+        <v>0</v>
+      </c>
+      <c r="R34" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S34" s="83">
+        <f t="shared" si="77"/>
+        <v>87.756249999999994</v>
+      </c>
+      <c r="T34" s="46">
+        <v>18</v>
+      </c>
+      <c r="U34" s="84">
+        <v>0.01</v>
+      </c>
+      <c r="V34" s="85">
+        <f>(S34*T34/1000)*(1+U34)</f>
+        <v>1.5954086249999999</v>
+      </c>
+      <c r="W34" s="53">
+        <v>360</v>
+      </c>
+      <c r="X34" s="54">
+        <v>50</v>
+      </c>
+      <c r="Y34" s="55">
+        <v>1.7728999999999999</v>
+      </c>
+      <c r="Z34" s="86">
+        <f t="shared" si="78"/>
+        <v>3.2831481481481482E-2</v>
+      </c>
+      <c r="AA34" s="87">
+        <f t="shared" si="79"/>
+        <v>0.01</v>
+      </c>
+      <c r="AB34" s="86">
+        <f t="shared" si="85"/>
+        <v>0.82899490740740744</v>
+      </c>
+      <c r="AC34" s="86">
+        <f t="shared" si="80"/>
+        <v>4.7862258749999997E-2</v>
+      </c>
+      <c r="AD34" s="86">
+        <f t="shared" si="81"/>
+        <v>6.6319592592592597E-2</v>
+      </c>
+      <c r="AE34" s="58">
+        <v>0.42</v>
+      </c>
+      <c r="AF34" s="87">
+        <f t="shared" si="82"/>
+        <v>0.10541548958977864</v>
+      </c>
+      <c r="AG34" s="58">
+        <v>0.3</v>
+      </c>
+      <c r="AH34" s="87">
+        <f t="shared" si="83"/>
+        <v>7.5296778278413315E-2</v>
+      </c>
+      <c r="AI34" s="86">
+        <f t="shared" si="86"/>
+        <v>0.48878780756249995</v>
+      </c>
+      <c r="AJ34" s="59">
+        <v>217500</v>
+      </c>
+      <c r="AK34" s="56">
+        <f>AJ34/918260</f>
+        <v>0.23686101975475354</v>
+      </c>
+      <c r="AL34" s="90">
+        <f t="shared" si="84"/>
+        <v>3.9842342110672533</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" ht="72">
+      <c r="A35" s="74">
+        <v>4</v>
+      </c>
+      <c r="B35" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="38">
+        <v>2</v>
+      </c>
+      <c r="H35" s="77">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>1.5</v>
+      </c>
+      <c r="J35" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K35" s="77">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L35" s="78">
+        <v>8</v>
+      </c>
+      <c r="M35" s="77">
+        <f t="shared" si="76"/>
+        <v>6400</v>
+      </c>
+      <c r="N35" s="79">
+        <v>78</v>
+      </c>
+      <c r="O35" s="80">
+        <v>11.7</v>
+      </c>
+      <c r="P35" s="81">
+        <v>0</v>
+      </c>
+      <c r="R35" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S35" s="83">
+        <f t="shared" si="77"/>
+        <v>87.756249999999994</v>
+      </c>
+      <c r="T35" s="46">
+        <v>18</v>
+      </c>
+      <c r="U35" s="84">
+        <v>0.01</v>
+      </c>
+      <c r="V35" s="85">
+        <f t="shared" ref="V35:V37" si="87">(S35*T35/1000)*(1+U35)</f>
+        <v>1.5954086249999999</v>
+      </c>
+      <c r="W35" s="53">
+        <v>360</v>
+      </c>
+      <c r="X35" s="54">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="55">
+        <v>1.7728999999999999</v>
+      </c>
+      <c r="Z35" s="86">
+        <f t="shared" si="78"/>
+        <v>3.2831481481481482E-2</v>
+      </c>
+      <c r="AA35" s="87">
+        <f t="shared" si="79"/>
+        <v>0.01</v>
+      </c>
+      <c r="AB35" s="86">
+        <f t="shared" si="85"/>
+        <v>0.82899490740740744</v>
+      </c>
+      <c r="AC35" s="86">
+        <f t="shared" si="80"/>
+        <v>4.7862258749999997E-2</v>
+      </c>
+      <c r="AD35" s="86">
+        <f t="shared" si="81"/>
+        <v>6.6319592592592597E-2</v>
+      </c>
+      <c r="AE35" s="58">
+        <v>0.42</v>
+      </c>
+      <c r="AF35" s="87">
+        <f t="shared" si="82"/>
+        <v>0.10541548958977864</v>
+      </c>
+      <c r="AG35" s="58">
+        <v>0.3</v>
+      </c>
+      <c r="AH35" s="87">
+        <f t="shared" si="83"/>
+        <v>7.5296778278413315E-2</v>
+      </c>
+      <c r="AI35" s="86">
+        <f t="shared" si="86"/>
+        <v>0.48878780756249995</v>
+      </c>
+      <c r="AJ35" s="59">
+        <v>217500</v>
+      </c>
+      <c r="AK35" s="56">
+        <f>AJ35/918260</f>
+        <v>0.23686101975475354</v>
+      </c>
+      <c r="AL35" s="90">
+        <f t="shared" si="84"/>
+        <v>3.9842342110672533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" ht="72">
+      <c r="A36" s="74">
+        <v>5</v>
+      </c>
+      <c r="B36" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="38">
+        <v>2</v>
+      </c>
+      <c r="H36" s="77">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>1.5</v>
+      </c>
+      <c r="J36" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K36" s="77">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L36" s="78">
+        <v>8</v>
+      </c>
+      <c r="M36" s="77">
+        <f t="shared" si="76"/>
+        <v>6400</v>
+      </c>
+      <c r="N36" s="79">
+        <v>27</v>
+      </c>
+      <c r="O36" s="80">
+        <v>4.8</v>
+      </c>
+      <c r="P36" s="81">
+        <v>0</v>
+      </c>
+      <c r="R36" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S36" s="83">
+        <f t="shared" si="77"/>
+        <v>33.306249999999999</v>
+      </c>
+      <c r="T36" s="46">
+        <v>18</v>
+      </c>
+      <c r="U36" s="84">
+        <v>0.01</v>
+      </c>
+      <c r="V36" s="85">
+        <f t="shared" si="87"/>
+        <v>0.60550762499999988</v>
+      </c>
+      <c r="W36" s="53">
+        <v>160</v>
+      </c>
+      <c r="X36" s="54">
+        <v>30</v>
+      </c>
+      <c r="Y36" s="55">
+        <v>1.0953999999999999</v>
+      </c>
+      <c r="Z36" s="86">
+        <f t="shared" si="78"/>
+        <v>2.028518518518518E-2</v>
+      </c>
+      <c r="AA36" s="87">
+        <f t="shared" si="79"/>
+        <v>0.01</v>
+      </c>
+      <c r="AB36" s="86">
+        <f t="shared" si="85"/>
+        <v>0.30732055555555549</v>
+      </c>
+      <c r="AC36" s="86">
+        <f t="shared" si="80"/>
+        <v>1.8165228749999995E-2</v>
+      </c>
+      <c r="AD36" s="86">
+        <f t="shared" si="81"/>
+        <v>2.458564444444444E-2</v>
+      </c>
+      <c r="AE36" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="AF36" s="87">
+        <f t="shared" si="82"/>
+        <v>6.6054198312676449E-2</v>
+      </c>
+      <c r="AG36" s="88">
+        <v>6.2E-2</v>
+      </c>
+      <c r="AH36" s="87">
+        <f t="shared" si="83"/>
+        <v>4.09536029538594E-2</v>
+      </c>
+      <c r="AI36" s="86">
+        <f t="shared" si="86"/>
+        <v>0.16763685806249995</v>
+      </c>
+      <c r="AJ36" s="89">
+        <f>140000*0.75</f>
+        <v>105000</v>
+      </c>
+      <c r="AK36" s="86">
+        <f>AJ36/(229566*2)</f>
+        <v>0.22869240218499254</v>
+      </c>
+      <c r="AL36" s="90">
+        <f t="shared" si="84"/>
+        <v>1.5139083139974923</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" ht="72">
+      <c r="A37" s="74">
+        <v>6</v>
+      </c>
+      <c r="B37" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="75" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="38">
+        <v>2</v>
+      </c>
+      <c r="H37" s="77">
+        <v>2</v>
+      </c>
+      <c r="I37">
+        <v>1.5</v>
+      </c>
+      <c r="J37" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="77">
+        <v>61.217799999999997</v>
+      </c>
+      <c r="L37" s="78">
+        <v>8</v>
+      </c>
+      <c r="M37" s="77">
+        <f t="shared" si="76"/>
+        <v>6400</v>
+      </c>
+      <c r="N37" s="79">
+        <v>27</v>
+      </c>
+      <c r="O37" s="80">
+        <v>4.8</v>
+      </c>
+      <c r="P37" s="81">
+        <v>0</v>
+      </c>
+      <c r="R37" s="49">
+        <v>25000</v>
+      </c>
+      <c r="S37" s="83">
+        <f t="shared" si="77"/>
+        <v>33.306249999999999</v>
+      </c>
+      <c r="T37" s="46">
+        <v>18</v>
+      </c>
+      <c r="U37" s="84">
+        <v>0.01</v>
+      </c>
+      <c r="V37" s="85">
+        <f t="shared" si="87"/>
+        <v>0.60550762499999988</v>
+      </c>
+      <c r="W37" s="53">
+        <v>160</v>
+      </c>
+      <c r="X37" s="54">
+        <v>30</v>
+      </c>
+      <c r="Y37" s="55">
+        <v>1.0953999999999999</v>
+      </c>
+      <c r="Z37" s="86">
+        <f t="shared" si="78"/>
+        <v>2.028518518518518E-2</v>
+      </c>
+      <c r="AA37" s="87">
+        <f t="shared" si="79"/>
+        <v>0.01</v>
+      </c>
+      <c r="AB37" s="86">
+        <f t="shared" si="85"/>
+        <v>0.30732055555555549</v>
+      </c>
+      <c r="AC37" s="86">
+        <f t="shared" si="80"/>
+        <v>1.8165228749999995E-2</v>
+      </c>
+      <c r="AD37" s="86">
+        <f t="shared" si="81"/>
+        <v>2.458564444444444E-2</v>
+      </c>
+      <c r="AE37" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="AF37" s="87">
+        <f t="shared" si="82"/>
+        <v>6.6054198312676449E-2</v>
+      </c>
+      <c r="AG37" s="88">
+        <v>6.2E-2</v>
+      </c>
+      <c r="AH37" s="87">
+        <f t="shared" si="83"/>
+        <v>4.09536029538594E-2</v>
+      </c>
+      <c r="AI37" s="86">
+        <f t="shared" si="86"/>
+        <v>0.16763685806249995</v>
+      </c>
+      <c r="AJ37" s="89">
+        <f>140000*0.75</f>
+        <v>105000</v>
+      </c>
+      <c r="AK37" s="86">
+        <f>AJ37/(229566*2)</f>
+        <v>0.22869240218499254</v>
+      </c>
+      <c r="AL37" s="90">
+        <f t="shared" si="84"/>
+        <v>1.5139083139974923</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="BA2:BB2"/>
